--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/13 19:21:10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3658</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>17261.9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3658</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.54</t>
+          <t>17261.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/15 13:43:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>145000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17261.9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17261.9</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/15 13:43:01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>17261</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10196</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>1171.95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17261</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.9</t>
+          <t>1171.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/17 17:19:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10196</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>10196</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1171.95</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1171.95</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/17 17:19:54</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1171</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9999</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>952.29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1171</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.95</t>
+          <t>952.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/18 19:11:40</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>9999</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>9999</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>952.29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>952.29</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/18 19:11:40</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>952</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>8641.98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>952</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.29</t>
+          <t>8641.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/19 16:32:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8641</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8641.98</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8641</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8641.98</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/19 16:32:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8641</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25998</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>2988.28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8641</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.98</t>
+          <t>2988.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/20 13:51:56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>25998</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>25998</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2988.28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2988.28</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/20 13:51:56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2988</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>33333.33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2988</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.28</t>
+          <t>33333.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/21 13:13:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>33333</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33333.33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>33333</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>33333.33</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/21 13:13:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>33333</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>43296</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>4976.55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33333</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.33</t>
+          <t>4976.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/23 18:15:32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>111889</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12860.8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/23 10:57:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>43296</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>4976.55</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>43296</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>155185</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17837.36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>4976.55</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17837.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/23 18:40:15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17837</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>155185</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17837.36</t>
+          <t>155185</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17837.36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17837</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17837.36</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/23 10:57:59</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>43296</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4976.55</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>17837</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>310000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>37125.75</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>155185</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17837.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17837</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.36</t>
+          <t>37125.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/24 19:45:39</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>37125</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>310000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>310000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37125.75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>37125</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>37125.75</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/24 19:45:39</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>37125</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>8199</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>942.41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37125</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.75</t>
+          <t>942.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/25 12:29:19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>17647.06</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/25 11:26:49</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>8199</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>942.41</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>8199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>158199</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18589.47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>942.41</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18589.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/25 14:55:19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18589</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>158199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18589.47</t>
+          <t>158199</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18589.47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18589</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>18589.47</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/25 11:26:49</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>8199</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>942.41</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18589</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>64794</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7447.59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>158199</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18589.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>18589</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.47</t>
+          <t>7447.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/26 14:24:59</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7447</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>64794</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>64794</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7447.59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7447</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7447.59</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/26 14:24:59</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7447</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>26997</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>3103.1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7447</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.59</t>
+          <t>3103.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/28 12:36:34</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9199</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1057.36</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/28 12:35:24</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>26997</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>3103.1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>26997</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>36196</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4160.46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3103.1</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4160.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/28 19:50:50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4160</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>36196</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4160.46</t>
+          <t>36196</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4160.46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4160</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4160.46</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/28 12:35:24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>26997</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3103.1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4160</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>60240.96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4160.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4160</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.46</t>
+          <t>60240.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/01 12:25:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20238.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/01 10:48:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>670000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80479.06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>60240.96</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80479.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/01 14:50:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>80479</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>670000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80479.06</t>
+          <t>670000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80479.06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80479</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>80479.06</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/01 10:48:59</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>60240.96</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>80479</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>32997</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3792.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>670000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>80479.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>80479</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.06</t>
+          <t>3792.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/02 19:08:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3792</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>32997</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>32997</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3792.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3792</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3792.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/02 19:08:01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3792</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9199</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>1057.36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3792</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>1057.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/06 21:12:37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>9199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>9199</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1057.36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1057.36</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/06 21:12:37</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>35294.12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1057</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.36</t>
+          <t>35294.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/07 15:29:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90909.09</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/07 12:40:00</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>35294.12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-    </row>
+          <t>10/07 15:29:48</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>35294.12</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>126203.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>35294.12</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>125615.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10/07 18:45:49</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>125615</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/07 15:29:48</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>126203.21</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>126203.21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>126203</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>125615.21</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/07 12:40:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>35294.12</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>125615</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>12999</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1494.14</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1100000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>126203.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>126203</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.21</t>
+          <t>1494.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/08 11:42:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>41000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5061.73</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/08 11:41:36</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>12999</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1494.14</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>12999</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1494.14</t>
+          <t>53999</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6555.87</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1494.14</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6555.87</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/08 16:54:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6555</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxzf0001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>53999</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6555.87</t>
+          <t>53999</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6555.87</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6555</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6555.87</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.87</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/08 11:42:30</t>
+          <t>10/09 11:17:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5061.73</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/08 11:41:36</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>12999</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1494.14</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6555</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxzf0001</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6555.87</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6555</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.87</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/09 14:19:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 11:17:22</t>
+          <t>10/10 10:51:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>1264.25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/09 14:19:05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10999</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1264.25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>1264.25</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -72,130 +72,115 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10/10 10:51:19</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>10999</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1264.25</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/11 14:24:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -215,7 +200,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -227,7 +212,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1264.25</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -239,7 +224,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1264</t>
         </is>
       </c>
     </row>
@@ -251,7 +236,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1264.25</t>
+          <t>-1264</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -157,45 +157,30 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10/11 14:24:40</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -207,7 +192,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -219,24 +204,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1264</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-1264</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10/15 11:34:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>35502.96</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35502.96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>35502.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/15 14:19:13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>35502</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>35502.96</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35502.96</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>35502</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>35502.96</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:34:44</t>
+          <t>10/17 10:38:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35502.96</t>
+          <t>5470.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/15 14:19:13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>35502</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>47597</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>5470.92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35502.96</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35502</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.96</t>
+          <t>5470.92</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/17 18:42:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5470</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>47597</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5470.92</t>
+          <t>47597</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5470.92</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5470</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5470.92</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.92</t>
         </is>
       </c>
     </row>
